--- a/applications/april/jobappstracka.xlsx
+++ b/applications/april/jobappstracka.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\resume\applications\april\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0D2DF60-73FB-4152-8531-266A821E3DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F02D57-8A93-45BC-A41E-75A99EA198CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31965" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{AB1376D1-AA26-43C8-B385-B9C7A7AE9DEC}"/>
+    <workbookView xWindow="-38520" yWindow="-165" windowWidth="38640" windowHeight="21120" xr2:uid="{AB1376D1-AA26-43C8-B385-B9C7A7AE9DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -122,9 +122,6 @@
     <t>cfan company</t>
   </si>
   <si>
-    <t>fansly</t>
-  </si>
-  <si>
     <t>card sorting and fulfillment associate</t>
   </si>
   <si>
@@ -135,13 +132,133 @@
   </si>
   <si>
     <t>team member</t>
+  </si>
+  <si>
+    <t>fansly / PACKZ</t>
+  </si>
+  <si>
+    <t>dealer tire llc</t>
+  </si>
+  <si>
+    <t>warehouse associate, driver</t>
+  </si>
+  <si>
+    <t>cohere</t>
+  </si>
+  <si>
+    <t>porter</t>
+  </si>
+  <si>
+    <t>kissing tree, tx</t>
+  </si>
+  <si>
+    <t>the chapel at gruene</t>
+  </si>
+  <si>
+    <t>strong table mover for weddings</t>
+  </si>
+  <si>
+    <t>little guys movers</t>
+  </si>
+  <si>
+    <t>driver, crew leader, mover</t>
+  </si>
+  <si>
+    <t>chillis</t>
+  </si>
+  <si>
+    <t>dishwasher</t>
+  </si>
+  <si>
+    <t>interview, good interview but conflicting schedules</t>
+  </si>
+  <si>
+    <t>awaiting further instruction after phone screen</t>
+  </si>
+  <si>
+    <t>2nd interview, but found out it is MLM</t>
+  </si>
+  <si>
+    <t>miller knoll / design within reach</t>
+  </si>
+  <si>
+    <t>club car wash</t>
+  </si>
+  <si>
+    <t>carwash attendant</t>
+  </si>
+  <si>
+    <t>manor, tx</t>
+  </si>
+  <si>
+    <t>tumble 22</t>
+  </si>
+  <si>
+    <t>sams club</t>
+  </si>
+  <si>
+    <t>produce associate</t>
+  </si>
+  <si>
+    <t>applied, scheduled interview, incompatibel schedule</t>
+  </si>
+  <si>
+    <t>applied, scheduled tour</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>applied, video call, awaiting further instructtion</t>
+  </si>
+  <si>
+    <t>phone screen, scheduled phone screen</t>
+  </si>
+  <si>
+    <t>applied in person, awaiting further instruction</t>
+  </si>
+  <si>
+    <t>applied, scheduled on site interview</t>
+  </si>
+  <si>
+    <t>applied, video call scheduled</t>
+  </si>
+  <si>
+    <t>hours</t>
+  </si>
+  <si>
+    <t>schedule</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>thur-Sunday, 11pm-2am</t>
+  </si>
+  <si>
+    <t>full-time?</t>
+  </si>
+  <si>
+    <t>full time 9-5</t>
+  </si>
+  <si>
+    <t>25-30</t>
+  </si>
+  <si>
+    <t>part-time</t>
+  </si>
+  <si>
+    <t>19.25-21.50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,8 +280,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,6 +305,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,19 +327,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -532,18 +681,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8900F695-D80A-4830-B1CB-C747223FB0FA}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
     <col min="2" max="2" width="42.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="57.42578125" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="32.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,8 +713,17 @@
       <c r="F1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -580,7 +740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -590,14 +750,20 @@
       <c r="C3" s="1">
         <v>46124</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
+      <c r="D3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46127</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -607,14 +773,14 @@
       <c r="C4" s="1">
         <v>46124</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
+      <c r="D4" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -631,7 +797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -641,14 +807,20 @@
       <c r="C6" s="1">
         <v>46124</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
+      <c r="D6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46127</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -665,7 +837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -675,14 +847,20 @@
       <c r="C8" s="1">
         <v>46124</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
+      <c r="D8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46127</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -699,7 +877,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -716,38 +894,250 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="1">
         <v>46125</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
+      <c r="D11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46126</v>
       </c>
       <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>46125</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46126</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46126</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46126</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/applications/april/jobappstracka.xlsx
+++ b/applications/april/jobappstracka.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon\Documents\resume\applications\april\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F02D57-8A93-45BC-A41E-75A99EA198CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E65329F-F9AD-454B-92DD-F4AFDAE86EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-165" windowWidth="38640" windowHeight="21120" xr2:uid="{AB1376D1-AA26-43C8-B385-B9C7A7AE9DEC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>COMPANY NAME</t>
   </si>
@@ -203,27 +203,12 @@
     <t>applied, scheduled interview, incompatibel schedule</t>
   </si>
   <si>
-    <t>applied, scheduled tour</t>
-  </si>
-  <si>
     <t>pay</t>
   </si>
   <si>
     <t>applied, video call, awaiting further instructtion</t>
   </si>
   <si>
-    <t>phone screen, scheduled phone screen</t>
-  </si>
-  <si>
-    <t>applied in person, awaiting further instruction</t>
-  </si>
-  <si>
-    <t>applied, scheduled on site interview</t>
-  </si>
-  <si>
-    <t>applied, video call scheduled</t>
-  </si>
-  <si>
     <t>hours</t>
   </si>
   <si>
@@ -252,13 +237,64 @@
   </si>
   <si>
     <t>19.25-21.50</t>
+  </si>
+  <si>
+    <t>mattres firm</t>
+  </si>
+  <si>
+    <t>warehouse associate 2</t>
+  </si>
+  <si>
+    <t>full-time</t>
+  </si>
+  <si>
+    <t>fedex</t>
+  </si>
+  <si>
+    <t>package handler</t>
+  </si>
+  <si>
+    <t>part-time like usual, hopefully the same hours</t>
+  </si>
+  <si>
+    <t>rejected for being unqualified, lol</t>
+  </si>
+  <si>
+    <t>2nd interview on 4/21</t>
+  </si>
+  <si>
+    <t>applied, video call scheduled for 4/20</t>
+  </si>
+  <si>
+    <t>applied in person, waiting for background check to go through</t>
+  </si>
+  <si>
+    <t>good phone screen, it asset management</t>
+  </si>
+  <si>
+    <t>application status has changed to "interviewing"</t>
+  </si>
+  <si>
+    <t>16-25</t>
+  </si>
+  <si>
+    <t>21-23</t>
+  </si>
+  <si>
+    <t>in the process of settinng up an interview</t>
+  </si>
+  <si>
+    <t>likely got approved awaiting the confirmation</t>
+  </si>
+  <si>
+    <t>passed phone screen, awaiting in-person interview</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,13 +305,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2D2D2D"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -330,20 +359,21 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -681,17 +711,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8900F695-D80A-4830-B1CB-C747223FB0FA}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.140625" customWidth="1"/>
     <col min="2" max="2" width="42.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" customWidth="1"/>
+    <col min="4" max="4" width="75.85546875" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="24.42578125" customWidth="1"/>
     <col min="7" max="7" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" customWidth="1"/>
+    <col min="9" max="9" width="61" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -714,13 +744,13 @@
         <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -741,26 +771,26 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
         <v>46124</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="D3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="5">
         <v>46127</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
-        <v>18</v>
+      <c r="G3" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -773,7 +803,7 @@
       <c r="C4" s="1">
         <v>46124</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F4" t="s">
@@ -799,345 +829,400 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>46124</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46127</v>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>21.63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>46124</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="7">
-        <v>46127</v>
+        <v>46125</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1">
         <v>46125</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46126</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
       </c>
       <c r="C11" s="1">
-        <v>46125</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1">
         <v>46126</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46126</v>
+      </c>
       <c r="F11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
-        <v>46125</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="1">
         <v>46126</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1">
         <v>46126</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="3"/>
       <c r="F13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1">
         <v>46126</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46127</v>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14">
-        <v>40</v>
-      </c>
-      <c r="I14" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46127</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="4">
+        <v>18</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="5">
+        <v>46128</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="5">
+        <v>46129</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="4">
+        <v>18.25</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46126</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="5">
+        <v>46127</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="4">
+        <v>40</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C19" s="7">
         <v>46126</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="7">
+      <c r="D19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="5">
         <v>46127</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G15">
+      <c r="G19" s="4">
         <v>25</v>
       </c>
-      <c r="H15">
+      <c r="H19" s="4">
         <v>12</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I19" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46126</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="5">
+        <v>46127</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="4">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4">
+        <v>40</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5">
+        <v>46124</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="5">
+        <v>46127</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="4">
+        <v>21.63</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46124</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="5">
+        <v>46127</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="5">
+        <v>46125</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="5">
         <v>46126</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16">
-        <v>18</v>
-      </c>
-      <c r="H16">
-        <v>40</v>
-      </c>
-      <c r="I16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="1">
-        <v>46126</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>25</v>
+      <c r="F23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
